--- a/data/trans_dic/P44A$endoscopia-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P44A$endoscopia-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han realizado al menos una endoscopia para detectar cáncer de colon</t>
+          <t>Población a la que le han realizado al menos una endoscopia para detectar cáncer de colon (tasa de respuesta: 98,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>28,35; 100,0</t>
+          <t>29,04; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,55; 56,87</t>
+          <t>14,16; 54,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21,96; 42,2</t>
+          <t>22,79; 40,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36,09; 92,62</t>
+          <t>40,62; 92,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,53; 68,37</t>
+          <t>13,6; 64,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,92; 35,31</t>
+          <t>14,68; 33,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,93; 89,73</t>
+          <t>48,12; 89,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,35; 52,26</t>
+          <t>20,22; 50,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>21,72; 36,44</t>
+          <t>22,3; 36,4</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>47,31; 91,01</t>
+          <t>49,15; 90,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>33,81; 100,0</t>
+          <t>32,21; 100,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22,64; 45,87</t>
+          <t>22,7; 46,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24,95; 67,99</t>
+          <t>25,11; 68,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,94; 100,0</t>
+          <t>17,57; 100,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,54; 50,26</t>
+          <t>26,97; 51,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,83; 75,63</t>
+          <t>44,12; 75,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>37,13; 88,11</t>
+          <t>37,67; 91,85</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>27,12; 44,81</t>
+          <t>27,39; 44,72</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,65; 82,36</t>
+          <t>12,67; 82,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,32; 57,71</t>
+          <t>16,48; 56,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30,4; 51,91</t>
+          <t>30,53; 51,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30,83; 91,69</t>
+          <t>30,36; 85,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,22; 54,41</t>
+          <t>5,18; 49,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,19; 40,49</t>
+          <t>22,9; 41,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33,69; 79,13</t>
+          <t>32,67; 76,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,2; 43,24</t>
+          <t>15,13; 43,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28,97; 42,73</t>
+          <t>29,74; 43,63</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,45; 90,44</t>
+          <t>21,68; 89,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>41,45; 78,35</t>
+          <t>39,04; 77,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34,89; 60,38</t>
+          <t>35,13; 58,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34,79; 91,31</t>
+          <t>35,05; 85,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>55,38; 95,13</t>
+          <t>59,79; 95,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,14; 59,53</t>
+          <t>42,27; 60,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,27; 81,77</t>
+          <t>39,23; 82,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>54,48; 83,11</t>
+          <t>55,84; 85,28</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>41,48; 56,63</t>
+          <t>41,33; 56,27</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>73,58; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1128,37 +1128,37 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53,04; 88,02</t>
+          <t>53,27; 90,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33,57; 100,0</t>
+          <t>33,81; 100,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>22,35; 100,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,78; 65,73</t>
+          <t>34,03; 66,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>65,97; 100,0</t>
+          <t>64,62; 100,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>27,71; 100,0</t>
+          <t>28,09; 100,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>49,82; 72,59</t>
+          <t>47,64; 72,43</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>31,5; 88,96</t>
+          <t>31,42; 88,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23,34; 87,16</t>
+          <t>23,55; 82,73</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>31,37; 56,97</t>
+          <t>31,67; 56,45</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16,85; 100,0</t>
+          <t>16,53; 100,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>25,03; 88,78</t>
+          <t>26,59; 88,92</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,98; 35,17</t>
+          <t>13,09; 34,02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38,86; 86,5</t>
+          <t>39,29; 86,51</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>32,88; 83,27</t>
+          <t>34,49; 78,84</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>26,43; 43,22</t>
+          <t>25,99; 42,96</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>40,48; 87,58</t>
+          <t>39,73; 88,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>50,92; 81,38</t>
+          <t>50,77; 81,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38,0; 55,63</t>
+          <t>37,1; 55,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>43,23; 89,02</t>
+          <t>38,79; 88,24</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>48,66; 85,13</t>
+          <t>47,85; 84,94</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,48; 41,22</t>
+          <t>28,18; 42,63</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,02; 82,27</t>
+          <t>48,38; 82,95</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>55,2; 78,32</t>
+          <t>54,29; 78,78</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>34,9; 46,16</t>
+          <t>34,91; 46,03</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>19,98; 61,12</t>
+          <t>22,03; 63,62</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>22,66; 62,98</t>
+          <t>21,78; 63,82</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>42,64; 95,32</t>
+          <t>42,56; 94,87</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21,56; 77,65</t>
+          <t>21,91; 77,82</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>18,35; 76,33</t>
+          <t>23,61; 75,84</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,41; 45,37</t>
+          <t>32,82; 45,05</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,93; 60,93</t>
+          <t>26,62; 59,0</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>26,13; 60,8</t>
+          <t>27,57; 60,44</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>40,01; 90,05</t>
+          <t>39,77; 91,61</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>51,6; 71,36</t>
+          <t>52,35; 71,18</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>44,01; 59,97</t>
+          <t>43,79; 60,1</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>41,3; 83,32</t>
+          <t>41,8; 82,21</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>51,77; 71,17</t>
+          <t>51,64; 71,54</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>45,85; 65,62</t>
+          <t>45,02; 65,99</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>33,06; 39,47</t>
+          <t>33,29; 39,62</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>54,6; 69,23</t>
+          <t>54,51; 68,0</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>47,22; 59,71</t>
+          <t>47,59; 59,97</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>38,95; 72,6</t>
+          <t>38,93; 74,85</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han realizado al menos una endoscopia para detectar cáncer de colon</t>
+          <t>Población a la que le han realizado al menos una endoscopia para detectar cáncer de colon (tasa de respuesta: 98,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1972; 6955</t>
+          <t>2020; 6955</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3635; 13292</t>
+          <t>3309; 12662</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16113; 30960</t>
+          <t>16717; 30015</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3995; 10253</t>
+          <t>4496; 10205</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2136; 10793</t>
+          <t>2148; 10174</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5239; 12404</t>
+          <t>5157; 11865</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8639; 16175</t>
+          <t>8673; 16162</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7577; 20465</t>
+          <t>7917; 19892</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>23565; 39538</t>
+          <t>24189; 39492</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11408; 21945</t>
+          <t>11851; 21909</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3151; 9319</t>
+          <t>3002; 9319</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14147; 28658</t>
+          <t>14181; 28909</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5093; 13879</t>
+          <t>5126; 13964</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1023; 5704</t>
+          <t>1002; 5704</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10884; 19862</t>
+          <t>10658; 20449</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19516; 33674</t>
+          <t>19646; 33609</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5578; 13236</t>
+          <t>5658; 13799</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27659; 45710</t>
+          <t>27940; 45613</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1166; 7593</t>
+          <t>1168; 7642</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3618; 12053</t>
+          <t>3441; 11761</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17268; 29482</t>
+          <t>17344; 29472</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4104; 12206</t>
+          <t>4041; 11409</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1042; 10857</t>
+          <t>1034; 9868</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12931; 22572</t>
+          <t>12769; 23122</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7591; 17828</t>
+          <t>7361; 17302</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5799; 17660</t>
+          <t>6180; 17945</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>32612; 48094</t>
+          <t>33476; 49107</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2342; 9875</t>
+          <t>2367; 9743</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10786; 20391</t>
+          <t>10160; 20290</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18392; 31827</t>
+          <t>18514; 30690</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4759; 12494</t>
+          <t>4796; 11651</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11308; 19427</t>
+          <t>12209; 19454</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24280; 35135</t>
+          <t>24944; 35494</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9907; 20115</t>
+          <t>9651; 20252</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25304; 38603</t>
+          <t>25937; 39609</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>46345; 63271</t>
+          <t>46172; 62867</t>
         </is>
       </c>
     </row>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4634; 6298</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2523,37 +2523,37 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6828; 11331</t>
+          <t>6858; 11698</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2204; 6566</t>
+          <t>2220; 6566</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3989</t>
+          <t>892; 3989</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4707; 9161</t>
+          <t>4743; 9223</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8486; 12864</t>
+          <t>8313; 12864</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1929; 6961</t>
+          <t>1955; 6961</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>13357; 19461</t>
+          <t>12773; 19418</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2913; 8227</t>
+          <t>2905; 8226</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2424; 9053</t>
+          <t>2446; 8593</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12214; 22181</t>
+          <t>12329; 21979</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1060; 6292</t>
+          <t>1040; 6292</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2154; 7640</t>
+          <t>2288; 7652</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3966; 10746</t>
+          <t>4000; 10395</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6039; 13442</t>
+          <t>6106; 13443</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6245; 15815</t>
+          <t>6550; 14973</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>18365; 30030</t>
+          <t>18061; 29849</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>6357; 13755</t>
+          <t>6239; 13829</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>20529; 32811</t>
+          <t>20470; 32806</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>40128; 58755</t>
+          <t>39182; 58346</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8894; 18313</t>
+          <t>7980; 18152</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>13720; 24006</t>
+          <t>13492; 23953</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>31359; 47035</t>
+          <t>32150; 48643</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17420; 29845</t>
+          <t>17549; 30093</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>37823; 53665</t>
+          <t>37200; 53981</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>76685; 101418</t>
+          <t>76706; 101127</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>5376; 16447</t>
+          <t>5928; 17119</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>5983; 16629</t>
+          <t>5752; 16852</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>159446; 356457</t>
+          <t>159154; 354756</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3244; 11683</t>
+          <t>3296; 11708</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2472; 10282</t>
+          <t>3180; 10216</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>42174; 59032</t>
+          <t>42697; 58616</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>12136; 25563</t>
+          <t>11170; 24754</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>10421; 24246</t>
+          <t>10994; 24101</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>201692; 453882</t>
+          <t>200470; 461755</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>56432; 78039</t>
+          <t>57249; 77847</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>70282; 95764</t>
+          <t>69928; 95964</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>320782; 647154</t>
+          <t>324645; 638546</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>55368; 76114</t>
+          <t>55232; 76516</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>53248; 76196</t>
+          <t>52283; 76630</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>158068; 188697</t>
+          <t>159143; 189444</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>118116; 149759</t>
+          <t>117916; 147087</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>130232; 164680</t>
+          <t>131253; 165398</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>488756; 910962</t>
+          <t>488561; 939193</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P44A$endoscopia-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P44A$endoscopia-Provincia-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>30,21%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>29,04; 100,0</t>
+          <t>28,61; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,16; 54,18</t>
+          <t>14,2; 54,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22,79; 40,91</t>
+          <t>24,85; 43,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40,62; 92,19</t>
+          <t>40,91; 92,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,6; 64,45</t>
+          <t>13,41; 66,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,68; 33,78</t>
+          <t>14,59; 33,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,12; 89,67</t>
+          <t>47,49; 89,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>20,22; 50,8</t>
+          <t>18,48; 49,99</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22,3; 36,4</t>
+          <t>23,95; 38,18</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>34,85%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>49,15; 90,86</t>
+          <t>48,87; 91,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>32,21; 100,0</t>
+          <t>31,56; 100,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22,7; 46,27</t>
+          <t>21,97; 45,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25,11; 68,41</t>
+          <t>25,24; 68,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,57; 100,0</t>
+          <t>17,75; 100,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,97; 51,75</t>
+          <t>26,19; 48,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,12; 75,48</t>
+          <t>43,95; 76,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>37,67; 91,85</t>
+          <t>40,74; 92,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>27,39; 44,72</t>
+          <t>26,99; 44,71</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>35,98%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,67; 82,89</t>
+          <t>12,67; 82,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,48; 56,31</t>
+          <t>16,67; 57,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30,53; 51,89</t>
+          <t>30,44; 52,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30,36; 85,7</t>
+          <t>26,7; 91,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,18; 49,46</t>
+          <t>5,58; 49,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,9; 41,47</t>
+          <t>22,67; 40,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32,67; 76,79</t>
+          <t>32,94; 77,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,13; 43,94</t>
+          <t>15,64; 45,96</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29,74; 43,63</t>
+          <t>28,83; 42,93</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>49,62%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,68; 89,23</t>
+          <t>22,1; 92,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>39,04; 77,96</t>
+          <t>40,79; 78,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35,13; 58,23</t>
+          <t>36,46; 60,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35,05; 85,15</t>
+          <t>33,79; 91,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>59,79; 95,26</t>
+          <t>59,89; 94,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,27; 60,14</t>
+          <t>42,31; 60,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,23; 82,32</t>
+          <t>39,14; 82,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>55,84; 85,28</t>
+          <t>55,95; 82,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>41,33; 56,27</t>
+          <t>41,27; 56,8</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>73,14%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>61,23%</t>
+          <t>60,54%</t>
         </is>
       </c>
     </row>
@@ -1128,37 +1128,37 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53,27; 90,87</t>
+          <t>50,87; 88,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33,81; 100,0</t>
+          <t>33,57; 100,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>22,35; 100,0</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,03; 66,18</t>
+          <t>32,95; 65,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,62; 100,0</t>
+          <t>58,72; 100,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>28,09; 100,0</t>
+          <t>27,76; 100,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>47,64; 72,43</t>
+          <t>48,58; 72,97</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>33,98%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>31,42; 88,94</t>
+          <t>22,58; 88,89</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23,55; 82,73</t>
+          <t>18,48; 89,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>31,67; 56,45</t>
+          <t>31,1; 54,75</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16,53; 100,0</t>
+          <t>16,57; 100,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>26,59; 88,92</t>
+          <t>25,09; 88,63</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13,09; 34,02</t>
+          <t>13,32; 33,92</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39,29; 86,51</t>
+          <t>39,33; 86,48</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>34,49; 78,84</t>
+          <t>31,49; 79,34</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>25,99; 42,96</t>
+          <t>25,58; 42,84</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>40,8%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>39,73; 88,05</t>
+          <t>37,53; 86,67</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>50,77; 81,37</t>
+          <t>51,97; 81,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>37,1; 55,25</t>
+          <t>38,46; 56,67</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38,79; 88,24</t>
+          <t>39,48; 88,47</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>47,85; 84,94</t>
+          <t>47,06; 84,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,18; 42,63</t>
+          <t>28,5; 41,37</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,38; 82,95</t>
+          <t>48,35; 83,6</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>54,29; 78,78</t>
+          <t>56,25; 79,63</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>34,91; 46,03</t>
+          <t>35,36; 46,62</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>41,77%</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>22,03; 63,62</t>
+          <t>21,25; 64,6</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>21,78; 63,82</t>
+          <t>21,12; 62,09</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>42,56; 94,87</t>
+          <t>38,14; 52,21</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21,91; 77,82</t>
+          <t>21,78; 78,36</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>23,61; 75,84</t>
+          <t>23,93; 76,52</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,82; 45,05</t>
+          <t>32,86; 45,22</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,62; 59,0</t>
+          <t>28,32; 59,86</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>27,57; 60,44</t>
+          <t>27,25; 61,67</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>39,77; 91,61</t>
+          <t>37,02; 46,5</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>39,99%</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>52,35; 71,18</t>
+          <t>50,73; 71,59</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>43,79; 60,1</t>
+          <t>43,78; 59,33</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>41,8; 82,21</t>
+          <t>39,24; 47,01</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>51,64; 71,54</t>
+          <t>51,54; 71,3</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>45,02; 65,99</t>
+          <t>45,67; 65,08</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>33,29; 39,62</t>
+          <t>33,4; 39,67</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>54,51; 68,0</t>
+          <t>54,16; 68,36</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>47,59; 59,97</t>
+          <t>47,5; 60,22</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>38,93; 74,85</t>
+          <t>37,66; 42,33</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22914</t>
+          <t>24459</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8240</t>
+          <t>8685</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>31154</t>
+          <t>33143</t>
         </is>
       </c>
     </row>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2020; 6955</t>
+          <t>1990; 6955</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3309; 12662</t>
+          <t>3319; 12830</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16717; 30015</t>
+          <t>18273; 31697</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4496; 10205</t>
+          <t>4529; 10252</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2148; 10174</t>
+          <t>2118; 10449</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5157; 11865</t>
+          <t>5276; 12195</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8673; 16162</t>
+          <t>8560; 16181</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7917; 19892</t>
+          <t>7237; 19573</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>24189; 39492</t>
+          <t>26277; 41880</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>21095</t>
+          <t>21794</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15126</t>
+          <t>15574</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>36220</t>
+          <t>37368</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11851; 21909</t>
+          <t>11783; 22006</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3002; 9319</t>
+          <t>2941; 9319</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14181; 28909</t>
+          <t>14287; 29353</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5126; 13964</t>
+          <t>5151; 13960</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1002; 5704</t>
+          <t>1013; 5704</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10658; 20449</t>
+          <t>11045; 20382</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19646; 33609</t>
+          <t>19569; 33920</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5658; 13799</t>
+          <t>6120; 13825</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27940; 45613</t>
+          <t>28939; 47930</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23379</t>
+          <t>22721</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17553</t>
+          <t>17882</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>40933</t>
+          <t>40604</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1168; 7642</t>
+          <t>1168; 7586</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3441; 11761</t>
+          <t>3483; 12004</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17344; 29472</t>
+          <t>16939; 29004</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4041; 11409</t>
+          <t>3555; 12204</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1034; 9868</t>
+          <t>1114; 9809</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12769; 23122</t>
+          <t>12967; 23192</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7361; 17302</t>
+          <t>7421; 17570</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6180; 17945</t>
+          <t>6388; 18771</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>33476; 49107</t>
+          <t>32537; 48446</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24586</t>
+          <t>28600</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30137</t>
+          <t>32377</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>54723</t>
+          <t>60977</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2367; 9743</t>
+          <t>2413; 10059</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10160; 20290</t>
+          <t>10615; 20557</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18514; 30690</t>
+          <t>21600; 35900</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4796; 11651</t>
+          <t>4623; 12500</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12209; 19454</t>
+          <t>12231; 19391</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24944; 35494</t>
+          <t>26926; 38478</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9651; 20252</t>
+          <t>9629; 20193</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25937; 39609</t>
+          <t>25988; 38334</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>46172; 62867</t>
+          <t>50712; 69796</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9496</t>
+          <t>9888</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6919</t>
+          <t>7222</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16415</t>
+          <t>17110</t>
         </is>
       </c>
     </row>
@@ -2523,37 +2523,37 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6858; 11698</t>
+          <t>6877; 11933</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2220; 6566</t>
+          <t>2204; 6566</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>892; 3989</t>
+          <t>0; 3989</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4743; 9223</t>
+          <t>4858; 9683</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8313; 12864</t>
+          <t>7554; 12864</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1955; 6961</t>
+          <t>1932; 6961</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>12773; 19418</t>
+          <t>13732; 20623</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>17008</t>
+          <t>16483</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6901</t>
+          <t>6916</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>23909</t>
+          <t>23399</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2905; 8226</t>
+          <t>2088; 8220</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2446; 8593</t>
+          <t>1920; 9263</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12329; 21979</t>
+          <t>11768; 20716</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1040; 6292</t>
+          <t>1042; 6292</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2288; 7652</t>
+          <t>2159; 7627</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4000; 10395</t>
+          <t>4132; 10526</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6106; 13443</t>
+          <t>6111; 13438</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6550; 14973</t>
+          <t>5979; 15067</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>18061; 29849</t>
+          <t>17616; 29501</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>49236</t>
+          <t>58105</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>39496</t>
+          <t>46477</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>88732</t>
+          <t>104582</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>6239; 13829</t>
+          <t>5893; 13611</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>20470; 32806</t>
+          <t>20955; 32759</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>39182; 58346</t>
+          <t>46754; 68893</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7980; 18152</t>
+          <t>8122; 18199</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>13492; 23953</t>
+          <t>13269; 23882</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>32150; 48643</t>
+          <t>38399; 55754</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17549; 30093</t>
+          <t>17538; 30328</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>37200; 53981</t>
+          <t>38538; 54562</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>76706; 101127</t>
+          <t>90628; 119504</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>302714</t>
+          <t>65352</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>49930</t>
+          <t>57052</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>352643</t>
+          <t>122405</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>5928; 17119</t>
+          <t>5718; 17384</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>5752; 16852</t>
+          <t>5576; 16396</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>159154; 354756</t>
+          <t>55107; 75438</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3296; 11708</t>
+          <t>3277; 11789</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>3180; 10216</t>
+          <t>3223; 10307</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>42697; 58616</t>
+          <t>48811; 67179</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>11170; 24754</t>
+          <t>11882; 25116</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>10994; 24101</t>
+          <t>10865; 24593</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>200470; 461755</t>
+          <t>108487; 136258</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>470429</t>
+          <t>247403</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>174304</t>
+          <t>192185</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>644732</t>
+          <t>439588</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>57249; 77847</t>
+          <t>55486; 78290</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>69928; 95964</t>
+          <t>69918; 94738</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>324645; 638546</t>
+          <t>224008; 268391</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>55232; 76516</t>
+          <t>55119; 76255</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>52283; 76630</t>
+          <t>53034; 75580</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>159143; 189444</t>
+          <t>176466; 209550</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>117916; 147087</t>
+          <t>117157; 147876</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>131253; 165398</t>
+          <t>131008; 166096</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>488561; 939193</t>
+          <t>413953; 465238</t>
         </is>
       </c>
     </row>
